--- a/College_Placement_Analytics.xlsx
+++ b/College_Placement_Analytics.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BE5A6D3-A2D1-4EBD-A7E0-1BE2646A63DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Placement_Data" sheetId="1" r:id="rId1"/>
@@ -24,9 +24,9 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Charts!$A$88:$B$133</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Placement_Data!$P$1:$P$501</definedName>
-    <definedName name="_xlcn.WorksheetConnection_College_Placement_Analytics_Realistic_500Rows.xlsxresult" hidden="1">result[]</definedName>
-    <definedName name="_xlcn.WorksheetConnection_College_Placement_Analytics_Realistic_500Rows.xlsxtblPlacement" hidden="1">tblPlacement[]</definedName>
-    <definedName name="_xlcn.WorksheetConnection_Placement_DataAN" hidden="1">Placement_Data!$A:$N</definedName>
+    <definedName name="_xlcn.WorksheetConnection_College_Placement_Analytics_Realistic_500Rows.xlsxresult1" hidden="1">result[]</definedName>
+    <definedName name="_xlcn.WorksheetConnection_College_Placement_Analytics_Realistic_500Rows.xlsxtblPlacement1" hidden="1">tblPlacement[]</definedName>
+    <definedName name="_xlcn.WorksheetConnection_Placement_DataAN1" hidden="1">Placement_Data!$A:$N</definedName>
     <definedName name="_xlnm.Extract" localSheetId="0">Placement_Data!$P$1</definedName>
     <definedName name="Slicer_Branch">#N/A</definedName>
     <definedName name="Slicer_Industry">#N/A</definedName>
@@ -98,7 +98,7 @@
     <extLst>
       <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{DE250136-89BD-433C-8126-D09CA5730AF9}">
         <x15:connection id="result">
-          <x15:rangePr sourceName="_xlcn.WorksheetConnection_College_Placement_Analytics_Realistic_500Rows.xlsxresult"/>
+          <x15:rangePr sourceName="_xlcn.WorksheetConnection_College_Placement_Analytics_Realistic_500Rows.xlsxresult1"/>
         </x15:connection>
       </ext>
     </extLst>
@@ -107,7 +107,7 @@
     <extLst>
       <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{DE250136-89BD-433C-8126-D09CA5730AF9}">
         <x15:connection id="tblPlacement" autoDelete="1">
-          <x15:rangePr sourceName="_xlcn.WorksheetConnection_College_Placement_Analytics_Realistic_500Rows.xlsxtblPlacement"/>
+          <x15:rangePr sourceName="_xlcn.WorksheetConnection_College_Placement_Analytics_Realistic_500Rows.xlsxtblPlacement1"/>
         </x15:connection>
       </ext>
     </extLst>
@@ -116,7 +116,7 @@
     <extLst>
       <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{DE250136-89BD-433C-8126-D09CA5730AF9}">
         <x15:connection id="Range" autoDelete="1">
-          <x15:rangePr sourceName="_xlcn.WorksheetConnection_Placement_DataAN"/>
+          <x15:rangePr sourceName="_xlcn.WorksheetConnection_Placement_DataAN1"/>
         </x15:connection>
       </ext>
     </extLst>
@@ -2359,6 +2359,15 @@
     <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2370,15 +2379,6 @@
     </xf>
     <xf numFmtId="9" fontId="9" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="2" fontId="9" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -20241,356 +20241,6 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{644F87F0-5E5C-4104-A24C-9C5C4ADF3533}" name="PivotTable8" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="CGPA Group">
-  <location ref="A146:C151" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="4">
-    <pivotField axis="axisRow" allDrilled="1" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" defaultAttributeDrillState="1">
-      <items count="4">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-      </items>
-    </pivotField>
-    <pivotField dataField="1" subtotalTop="0" showAll="0" defaultSubtotal="0"/>
-    <pivotField dataField="1" subtotalTop="0" showAll="0" defaultSubtotal="0"/>
-    <pivotField allDrilled="1" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" defaultAttributeDrillState="1"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="0"/>
-  </rowFields>
-  <rowItems count="5">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="-2"/>
-  </colFields>
-  <colItems count="2">
-    <i>
-      <x/>
-    </i>
-    <i i="1">
-      <x v="1"/>
-    </i>
-  </colItems>
-  <dataFields count="2">
-    <dataField name="Count of Student_ID" fld="1" subtotal="count" baseField="0" baseItem="0"/>
-    <dataField name="Sum of Placement Indicator" fld="2" baseField="0" baseItem="0"/>
-  </dataFields>
-  <pivotHierarchies count="38">
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy multipleItemSelectionAllowed="1" dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy multipleItemSelectionAllowed="1" dragToData="1"/>
-    <pivotHierarchy multipleItemSelectionAllowed="1" dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy multipleItemSelectionAllowed="1" dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-  </pivotHierarchies>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <rowHierarchiesUsage count="1">
-    <rowHierarchyUsage hierarchyUsage="11"/>
-  </rowHierarchiesUsage>
-  <colHierarchiesUsage count="1">
-    <colHierarchyUsage hierarchyUsage="-2"/>
-  </colHierarchiesUsage>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" calculatedMembersInFilters="1" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{E67621CE-5B39-4880-91FE-76760E9C1902}">
-      <x15:pivotTableUISettings sourceDataName="WorksheetConnection_Placement_Data!$A:$N">
-        <x15:activeTabTopLevelEntity name="[Range]"/>
-      </x15:pivotTableUISettings>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16 EnabledSubtotalsDefault="0" SubtotalsOnTopDefault="0"/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A4CD06D4-0333-4FF9-A121-EEEA4B59A04A}" name="PivotTable6" cacheId="6" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Industry">
-  <location ref="A132:C141" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="4">
-    <pivotField axis="axisRow" allDrilled="1" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" defaultAttributeDrillState="1">
-      <items count="8">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-      </items>
-    </pivotField>
-    <pivotField dataField="1" subtotalTop="0" showAll="0" defaultSubtotal="0"/>
-    <pivotField dataField="1" subtotalTop="0" showAll="0" defaultSubtotal="0"/>
-    <pivotField allDrilled="1" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" defaultAttributeDrillState="1"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="0"/>
-  </rowFields>
-  <rowItems count="9">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="6"/>
-    </i>
-    <i>
-      <x v="7"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="-2"/>
-  </colFields>
-  <colItems count="2">
-    <i>
-      <x/>
-    </i>
-    <i i="1">
-      <x v="1"/>
-    </i>
-  </colItems>
-  <dataFields count="2">
-    <dataField name="Count of Student_ID" fld="1" subtotal="count" baseField="0" baseItem="0"/>
-    <dataField name="Average of Package_LPA" fld="2" subtotal="average" baseField="0" baseItem="0"/>
-  </dataFields>
-  <pivotHierarchies count="38">
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy multipleItemSelectionAllowed="1" dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy multipleItemSelectionAllowed="1" dragToData="1"/>
-    <pivotHierarchy multipleItemSelectionAllowed="1" dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy multipleItemSelectionAllowed="1" dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1" caption="Average of Package_LPA"/>
-  </pivotHierarchies>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <rowHierarchiesUsage count="1">
-    <rowHierarchyUsage hierarchyUsage="8"/>
-  </rowHierarchiesUsage>
-  <colHierarchiesUsage count="1">
-    <colHierarchyUsage hierarchyUsage="-2"/>
-  </colHierarchiesUsage>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" calculatedMembersInFilters="1" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{E67621CE-5B39-4880-91FE-76760E9C1902}">
-      <x15:pivotTableUISettings sourceDataName="WorksheetConnection_Placement_Data!$A:$N">
-        <x15:activeTabTopLevelEntity name="[Range]"/>
-      </x15:pivotTableUISettings>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16 EnabledSubtotalsDefault="0" SubtotalsOnTopDefault="0"/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C99FBEF1-12B5-4A16-919A-46EE9B3976C5}" name="PivotTable2" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Internship Status">
-  <location ref="A17:C20" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="4">
-    <pivotField axis="axisRow" allDrilled="1" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" defaultAttributeDrillState="1">
-      <items count="2">
-        <item x="0"/>
-        <item x="1"/>
-      </items>
-    </pivotField>
-    <pivotField dataField="1" subtotalTop="0" showAll="0" defaultSubtotal="0"/>
-    <pivotField dataField="1" subtotalTop="0" showAll="0" defaultSubtotal="0"/>
-    <pivotField allDrilled="1" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" defaultAttributeDrillState="1"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="0"/>
-  </rowFields>
-  <rowItems count="3">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="-2"/>
-  </colFields>
-  <colItems count="2">
-    <i>
-      <x/>
-    </i>
-    <i i="1">
-      <x v="1"/>
-    </i>
-  </colItems>
-  <dataFields count="2">
-    <dataField name="Count of Student_ID" fld="1" subtotal="count" baseField="0" baseItem="0"/>
-    <dataField name="Sum of Placement Indicator" fld="2" baseField="0" baseItem="0"/>
-  </dataFields>
-  <pivotHierarchies count="38">
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy multipleItemSelectionAllowed="1" dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy multipleItemSelectionAllowed="1" dragToData="1"/>
-    <pivotHierarchy multipleItemSelectionAllowed="1" dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy multipleItemSelectionAllowed="1" dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-  </pivotHierarchies>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <rowHierarchiesUsage count="1">
-    <rowHierarchyUsage hierarchyUsage="3"/>
-  </rowHierarchiesUsage>
-  <colHierarchiesUsage count="1">
-    <colHierarchyUsage hierarchyUsage="-2"/>
-  </colHierarchiesUsage>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" calculatedMembersInFilters="1" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{E67621CE-5B39-4880-91FE-76760E9C1902}">
-      <x15:pivotTableUISettings sourceDataName="WorksheetConnection_Placement_Data!$A:$N">
-        <x15:activeTabTopLevelEntity name="[Range]"/>
-      </x15:pivotTableUISettings>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16 EnabledSubtotalsDefault="0" SubtotalsOnTopDefault="0"/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{8BB43561-78DE-4EED-B9A7-0BFBCBD27684}" name="PivotTable5" cacheId="5" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Companies">
   <location ref="A81:B127" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="3">
@@ -20855,7 +20505,7 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{5A2DD5E5-885B-4F4E-9E53-F086DA45E010}" name="PivotTable4" cacheId="4" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Branch">
   <location ref="A68:B76" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="3">
@@ -20968,7 +20618,7 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{F9404FE3-23DB-45A7-A558-3948BA4171E0}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" subtotalHiddenItems="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Branch">
   <location ref="A3:C11" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="4">
@@ -21094,7 +20744,251 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{644F87F0-5E5C-4104-A24C-9C5C4ADF3533}" name="PivotTable8" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="CGPA Group">
+  <location ref="A146:C151" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="4">
+    <pivotField axis="axisRow" allDrilled="1" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" defaultAttributeDrillState="1">
+      <items count="4">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" subtotalTop="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField dataField="1" subtotalTop="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField allDrilled="1" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" defaultAttributeDrillState="1"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="0"/>
+  </rowFields>
+  <rowItems count="5">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="-2"/>
+  </colFields>
+  <colItems count="2">
+    <i>
+      <x/>
+    </i>
+    <i i="1">
+      <x v="1"/>
+    </i>
+  </colItems>
+  <dataFields count="2">
+    <dataField name="Count of Student_ID" fld="1" subtotal="count" baseField="0" baseItem="0"/>
+    <dataField name="Sum of Placement Indicator" fld="2" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotHierarchies count="38">
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy multipleItemSelectionAllowed="1" dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy multipleItemSelectionAllowed="1" dragToData="1"/>
+    <pivotHierarchy multipleItemSelectionAllowed="1" dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy multipleItemSelectionAllowed="1" dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+  </pivotHierarchies>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <rowHierarchiesUsage count="1">
+    <rowHierarchyUsage hierarchyUsage="11"/>
+  </rowHierarchiesUsage>
+  <colHierarchiesUsage count="1">
+    <colHierarchyUsage hierarchyUsage="-2"/>
+  </colHierarchiesUsage>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" calculatedMembersInFilters="1" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{E67621CE-5B39-4880-91FE-76760E9C1902}">
+      <x15:pivotTableUISettings sourceDataName="WorksheetConnection_Placement_Data!$A:$N">
+        <x15:activeTabTopLevelEntity name="[Range]"/>
+      </x15:pivotTableUISettings>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16 EnabledSubtotalsDefault="0" SubtotalsOnTopDefault="0"/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A4CD06D4-0333-4FF9-A121-EEEA4B59A04A}" name="PivotTable6" cacheId="6" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Industry">
+  <location ref="A132:C141" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="4">
+    <pivotField axis="axisRow" allDrilled="1" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" defaultAttributeDrillState="1">
+      <items count="8">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" subtotalTop="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField dataField="1" subtotalTop="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField allDrilled="1" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" defaultAttributeDrillState="1"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="0"/>
+  </rowFields>
+  <rowItems count="9">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="-2"/>
+  </colFields>
+  <colItems count="2">
+    <i>
+      <x/>
+    </i>
+    <i i="1">
+      <x v="1"/>
+    </i>
+  </colItems>
+  <dataFields count="2">
+    <dataField name="Count of Student_ID" fld="1" subtotal="count" baseField="0" baseItem="0"/>
+    <dataField name="Average of Package_LPA" fld="2" subtotal="average" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotHierarchies count="38">
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy multipleItemSelectionAllowed="1" dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy multipleItemSelectionAllowed="1" dragToData="1"/>
+    <pivotHierarchy multipleItemSelectionAllowed="1" dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy multipleItemSelectionAllowed="1" dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1" caption="Average of Package_LPA"/>
+  </pivotHierarchies>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <rowHierarchiesUsage count="1">
+    <rowHierarchyUsage hierarchyUsage="8"/>
+  </rowHierarchiesUsage>
+  <colHierarchiesUsage count="1">
+    <colHierarchyUsage hierarchyUsage="-2"/>
+  </colHierarchiesUsage>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" calculatedMembersInFilters="1" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{E67621CE-5B39-4880-91FE-76760E9C1902}">
+      <x15:pivotTableUISettings sourceDataName="WorksheetConnection_Placement_Data!$A:$N">
+        <x15:activeTabTopLevelEntity name="[Range]"/>
+      </x15:pivotTableUISettings>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16 EnabledSubtotalsDefault="0" SubtotalsOnTopDefault="0"/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{8A5F2A46-50F5-45A4-A29F-B17730367707}" name="PivotTable3" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Skill">
   <location ref="A25:C63" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="3">
@@ -21319,6 +21213,112 @@
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <rowHierarchiesUsage count="1">
     <rowHierarchyUsage hierarchyUsage="4"/>
+  </rowHierarchiesUsage>
+  <colHierarchiesUsage count="1">
+    <colHierarchyUsage hierarchyUsage="-2"/>
+  </colHierarchiesUsage>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" calculatedMembersInFilters="1" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{E67621CE-5B39-4880-91FE-76760E9C1902}">
+      <x15:pivotTableUISettings sourceDataName="WorksheetConnection_Placement_Data!$A:$N">
+        <x15:activeTabTopLevelEntity name="[Range]"/>
+      </x15:pivotTableUISettings>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16 EnabledSubtotalsDefault="0" SubtotalsOnTopDefault="0"/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C99FBEF1-12B5-4A16-919A-46EE9B3976C5}" name="PivotTable2" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Internship Status">
+  <location ref="A17:C20" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="4">
+    <pivotField axis="axisRow" allDrilled="1" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" defaultAttributeDrillState="1">
+      <items count="2">
+        <item x="0"/>
+        <item x="1"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" subtotalTop="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField dataField="1" subtotalTop="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField allDrilled="1" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" defaultAttributeDrillState="1"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="0"/>
+  </rowFields>
+  <rowItems count="3">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="-2"/>
+  </colFields>
+  <colItems count="2">
+    <i>
+      <x/>
+    </i>
+    <i i="1">
+      <x v="1"/>
+    </i>
+  </colItems>
+  <dataFields count="2">
+    <dataField name="Count of Student_ID" fld="1" subtotal="count" baseField="0" baseItem="0"/>
+    <dataField name="Sum of Placement Indicator" fld="2" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotHierarchies count="38">
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy multipleItemSelectionAllowed="1" dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy multipleItemSelectionAllowed="1" dragToData="1"/>
+    <pivotHierarchy multipleItemSelectionAllowed="1" dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy multipleItemSelectionAllowed="1" dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+  </pivotHierarchies>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <rowHierarchiesUsage count="1">
+    <rowHierarchyUsage hierarchyUsage="3"/>
   </rowHierarchiesUsage>
   <colHierarchiesUsage count="1">
     <colHierarchyUsage hierarchyUsage="-2"/>
@@ -49047,7 +49047,7 @@
       </c>
       <c r="B1" s="16"/>
       <c r="C1" s="16"/>
-      <c r="E1" s="20">
+      <c r="E1" s="23">
         <f>KPI_Calculations!B3</f>
         <v>0.65</v>
       </c>
@@ -49107,31 +49107,31 @@
       <c r="S3" s="16"/>
     </row>
     <row r="4" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="17" t="s">
+      <c r="A4" s="20" t="s">
         <v>621</v>
       </c>
-      <c r="B4" s="18"/>
-      <c r="C4" s="19"/>
-      <c r="E4" s="21" t="s">
+      <c r="B4" s="21"/>
+      <c r="C4" s="22"/>
+      <c r="E4" s="17" t="s">
         <v>652</v>
       </c>
-      <c r="F4" s="22"/>
-      <c r="G4" s="23"/>
-      <c r="I4" s="21" t="s">
+      <c r="F4" s="18"/>
+      <c r="G4" s="19"/>
+      <c r="I4" s="17" t="s">
         <v>653</v>
       </c>
-      <c r="J4" s="22"/>
-      <c r="K4" s="23"/>
-      <c r="M4" s="21" t="s">
+      <c r="J4" s="18"/>
+      <c r="K4" s="19"/>
+      <c r="M4" s="17" t="s">
         <v>626</v>
       </c>
-      <c r="N4" s="22"/>
-      <c r="O4" s="23"/>
-      <c r="Q4" s="21" t="s">
+      <c r="N4" s="18"/>
+      <c r="O4" s="19"/>
+      <c r="Q4" s="17" t="s">
         <v>625</v>
       </c>
-      <c r="R4" s="22"/>
-      <c r="S4" s="23"/>
+      <c r="R4" s="18"/>
+      <c r="S4" s="19"/>
     </row>
     <row r="20" spans="29:29" x14ac:dyDescent="0.35">
       <c r="AC20" t="s">
